--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="911">
   <si>
     <t>#</t>
   </si>
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-23 06:14:44 UTC</t>
+    <t>2026-06-23 10:06:42 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>
@@ -1216,348 +1216,348 @@
     <t>RULE-SEC-151</t>
   </si>
   <si>
+    <t>Semgrep static analyzer checked rule #151: Validate codebase against vulnerability pattern in SQL Injection check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-152</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #152: Validate codebase against vulnerability pattern in Path Traversal check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-153</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #153: Validate codebase against vulnerability pattern in CSRF vulnerability</t>
+  </si>
+  <si>
+    <t>RULE-SEC-154</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #154: Validate codebase against vulnerability pattern in Broken Auth check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-155</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #155: Validate codebase against vulnerability pattern in CORS Configuration</t>
+  </si>
+  <si>
+    <t>RULE-SEC-156</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #156: Validate codebase against vulnerability pattern in Cryptography strengths</t>
+  </si>
+  <si>
+    <t>RULE-SEC-157</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #157: Validate codebase against vulnerability pattern in Database validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-158</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #158: Validate codebase against vulnerability pattern in Secrets leakage search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-159</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #159: Validate codebase against vulnerability pattern in Code execution safety</t>
+  </si>
+  <si>
+    <t>RULE-SEC-160</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #160: Validate codebase against vulnerability pattern in XSS Prevention</t>
+  </si>
+  <si>
+    <t>RULE-SEC-161</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #161: Validate codebase against vulnerability pattern in SQL Injection check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-162</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #162: Validate codebase against vulnerability pattern in Path Traversal check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-163</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #163: Validate codebase against vulnerability pattern in CSRF vulnerability</t>
+  </si>
+  <si>
+    <t>RULE-SEC-164</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #164: Validate codebase against vulnerability pattern in Broken Auth check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-165</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #165: Validate codebase against vulnerability pattern in CORS Configuration</t>
+  </si>
+  <si>
+    <t>RULE-SEC-166</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #166: Validate codebase against vulnerability pattern in Cryptography strengths</t>
+  </si>
+  <si>
+    <t>RULE-SEC-167</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #167: Validate codebase against vulnerability pattern in Database validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-168</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #168: Validate codebase against vulnerability pattern in Secrets leakage search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-169</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #169: Validate codebase against vulnerability pattern in Code execution safety</t>
+  </si>
+  <si>
+    <t>RULE-SEC-170</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #170: Validate codebase against vulnerability pattern in XSS Prevention</t>
+  </si>
+  <si>
+    <t>RULE-SEC-171</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #171: Validate codebase against vulnerability pattern in SQL Injection check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-172</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #172: Validate codebase against vulnerability pattern in Path Traversal check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-173</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #173: Validate codebase against vulnerability pattern in CSRF vulnerability</t>
+  </si>
+  <si>
+    <t>RULE-SEC-174</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #174: Validate codebase against vulnerability pattern in Broken Auth check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-175</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #175: Validate codebase against vulnerability pattern in CORS Configuration</t>
+  </si>
+  <si>
+    <t>RULE-SEC-176</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #176: Validate codebase against vulnerability pattern in Cryptography strengths</t>
+  </si>
+  <si>
+    <t>RULE-SEC-177</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #177: Validate codebase against vulnerability pattern in Database validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-178</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #178: Validate codebase against vulnerability pattern in Secrets leakage search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-179</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #179: Validate codebase against vulnerability pattern in Code execution safety</t>
+  </si>
+  <si>
+    <t>RULE-SEC-180</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #180: Validate codebase against vulnerability pattern in XSS Prevention</t>
+  </si>
+  <si>
+    <t>RULE-SEC-181</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #181: Validate codebase against vulnerability pattern in SQL Injection check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-182</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #182: Validate codebase against vulnerability pattern in Path Traversal check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-183</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #183: Validate codebase against vulnerability pattern in CSRF vulnerability</t>
+  </si>
+  <si>
+    <t>RULE-SEC-184</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #184: Validate codebase against vulnerability pattern in Broken Auth check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-185</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #185: Validate codebase against vulnerability pattern in CORS Configuration</t>
+  </si>
+  <si>
+    <t>RULE-SEC-186</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #186: Validate codebase against vulnerability pattern in Cryptography strengths</t>
+  </si>
+  <si>
+    <t>RULE-SEC-187</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #187: Validate codebase against vulnerability pattern in Database validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-188</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #188: Validate codebase against vulnerability pattern in Secrets leakage search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-189</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #189: Validate codebase against vulnerability pattern in Code execution safety</t>
+  </si>
+  <si>
+    <t>RULE-SEC-190</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #190: Validate codebase against vulnerability pattern in XSS Prevention</t>
+  </si>
+  <si>
+    <t>RULE-SEC-191</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #191: Validate codebase against vulnerability pattern in SQL Injection check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-192</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #192: Validate codebase against vulnerability pattern in Path Traversal check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-193</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #193: Validate codebase against vulnerability pattern in CSRF vulnerability</t>
+  </si>
+  <si>
+    <t>RULE-SEC-194</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #194: Validate codebase against vulnerability pattern in Broken Auth check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-195</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #195: Validate codebase against vulnerability pattern in CORS Configuration</t>
+  </si>
+  <si>
+    <t>RULE-SEC-196</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #196: Validate codebase against vulnerability pattern in Cryptography strengths</t>
+  </si>
+  <si>
+    <t>RULE-SEC-197</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #197: Validate codebase against vulnerability pattern in Database validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-198</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #198: Validate codebase against vulnerability pattern in Secrets leakage search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-199</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #199: Validate codebase against vulnerability pattern in Code execution safety</t>
+  </si>
+  <si>
+    <t>RULE-SEC-200</t>
+  </si>
+  <si>
+    <t>Semgrep static analyzer checked rule #200: Validate codebase against vulnerability pattern in XSS Prevention</t>
+  </si>
+  <si>
+    <t>RULE-SEC-201</t>
+  </si>
+  <si>
     <t>SCA (Dependency)</t>
   </si>
   <si>
     <t>Critical vulnerability check</t>
   </si>
   <si>
-    <t>Trivy dependency analyzer check #151: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-152</t>
+    <t>Trivy dependency analyzer check #201: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-202</t>
   </si>
   <si>
     <t>High vulnerability check</t>
   </si>
   <si>
-    <t>Trivy dependency analyzer check #152: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-153</t>
+    <t>Trivy dependency analyzer check #202: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-203</t>
   </si>
   <si>
     <t>License check</t>
   </si>
   <si>
-    <t>Trivy dependency analyzer check #153: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-154</t>
+    <t>Trivy dependency analyzer check #203: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-204</t>
   </si>
   <si>
     <t>Known exploit database lookup</t>
   </si>
   <si>
-    <t>Trivy dependency analyzer check #154: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-155</t>
+    <t>Trivy dependency analyzer check #204: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-205</t>
   </si>
   <si>
     <t>Outdated package check</t>
   </si>
   <si>
-    <t>Trivy dependency analyzer check #155: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-156</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #156: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-157</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #157: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-158</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #158: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-159</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #159: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-160</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #160: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-161</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #161: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-162</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #162: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-163</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #163: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-164</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #164: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-165</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #165: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-166</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #166: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-167</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #167: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-168</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #168: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-169</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #169: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-170</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #170: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-171</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #171: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-172</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #172: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-173</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #173: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-174</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #174: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-175</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #175: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-176</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #176: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-177</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #177: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-178</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #178: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-179</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #179: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-180</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #180: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-181</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #181: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-182</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #182: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-183</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #183: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-184</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #184: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-185</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #185: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-186</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #186: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-187</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #187: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-188</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #188: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-189</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #189: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-190</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #190: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-191</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #191: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-192</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #192: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-193</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #193: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-194</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #194: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-195</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #195: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-196</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #196: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-197</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #197: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-198</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #198: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-199</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #199: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-200</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #200: Audit package manifest file for Outdated package check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-201</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #201: Audit package manifest file for Critical vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-202</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #202: Audit package manifest file for High vulnerability check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-203</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #203: Audit package manifest file for License check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-204</t>
-  </si>
-  <si>
-    <t>Trivy dependency analyzer check #204: Audit package manifest file for Known exploit database lookup</t>
-  </si>
-  <si>
-    <t>RULE-SEC-205</t>
-  </si>
-  <si>
     <t>Trivy dependency analyzer check #205: Audit package manifest file for Outdated package check</t>
   </si>
   <si>
@@ -1834,319 +1834,919 @@
     <t>RULE-SEC-251</t>
   </si>
   <si>
+    <t>Trivy dependency analyzer check #251: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-252</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #252: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-253</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #253: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-254</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #254: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-255</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #255: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-256</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #256: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-257</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #257: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-258</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #258: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-259</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #259: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-260</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #260: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-261</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #261: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-262</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #262: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-263</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #263: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-264</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #264: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-265</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #265: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-266</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #266: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-267</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #267: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-268</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #268: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-269</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #269: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-270</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #270: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-271</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #271: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-272</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #272: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-273</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #273: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-274</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #274: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-275</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #275: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-276</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #276: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-277</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #277: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-278</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #278: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-279</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #279: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-280</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #280: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-281</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #281: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-282</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #282: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-283</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #283: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-284</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #284: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-285</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #285: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-286</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #286: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-287</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #287: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-288</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #288: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-289</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #289: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-290</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #290: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-291</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #291: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-292</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #292: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-293</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #293: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-294</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #294: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-295</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #295: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-296</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #296: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-297</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #297: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-298</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #298: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-299</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #299: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-300</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #300: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-301</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #301: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-302</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #302: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-303</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #303: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-304</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #304: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-305</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #305: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-306</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #306: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-307</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #307: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-308</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #308: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-309</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #309: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-310</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #310: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-311</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #311: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-312</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #312: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-313</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #313: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-314</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #314: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-315</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #315: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-316</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #316: Audit package manifest file for Critical vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-317</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #317: Audit package manifest file for High vulnerability check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-318</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #318: Audit package manifest file for License check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-319</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #319: Audit package manifest file for Known exploit database lookup</t>
+  </si>
+  <si>
+    <t>RULE-SEC-320</t>
+  </si>
+  <si>
+    <t>Trivy dependency analyzer check #320: Audit package manifest file for Outdated package check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-321</t>
+  </si>
+  <si>
     <t>Secrets</t>
   </si>
   <si>
     <t>MongoDB URI credentials</t>
   </si>
   <si>
-    <t>Gitleaks full-history scanner signature rule #251: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-252</t>
+    <t>Gitleaks full-history scanner signature rule #321: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-322</t>
   </si>
   <si>
     <t>PrivateKey header search</t>
   </si>
   <si>
-    <t>Gitleaks full-history scanner signature rule #252: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-253</t>
+    <t>Gitleaks full-history scanner signature rule #322: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-323</t>
   </si>
   <si>
     <t>GitHub Token signature</t>
   </si>
   <si>
-    <t>Gitleaks full-history scanner signature rule #253: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-254</t>
+    <t>Gitleaks full-history scanner signature rule #323: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-324</t>
   </si>
   <si>
     <t>SMTP Password check</t>
   </si>
   <si>
-    <t>Gitleaks full-history scanner signature rule #254: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-255</t>
+    <t>Gitleaks full-history scanner signature rule #324: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-325</t>
   </si>
   <si>
     <t>JWT validation check</t>
   </si>
   <si>
-    <t>Gitleaks full-history scanner signature rule #255: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-256</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #256: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-257</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #257: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-258</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #258: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-259</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #259: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-260</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #260: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-261</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #261: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-262</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #262: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-263</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #263: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-264</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #264: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-265</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #265: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-266</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #266: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-267</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #267: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-268</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #268: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-269</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #269: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-270</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #270: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-271</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #271: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-272</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #272: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-273</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #273: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-274</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #274: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-275</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #275: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-276</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #276: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-277</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #277: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-278</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #278: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-279</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #279: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-280</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #280: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-281</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #281: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-282</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #282: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-283</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #283: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-284</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #284: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-285</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #285: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-286</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #286: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-287</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #287: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-288</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #288: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-289</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #289: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-290</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #290: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-291</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #291: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-292</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #292: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-293</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #293: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-294</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #294: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-295</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #295: Identify leaks matching JWT validation check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-296</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #296: Identify leaks matching MongoDB URI credentials</t>
-  </si>
-  <si>
-    <t>RULE-SEC-297</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #297: Identify leaks matching PrivateKey header search</t>
-  </si>
-  <si>
-    <t>RULE-SEC-298</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #298: Identify leaks matching GitHub Token signature</t>
-  </si>
-  <si>
-    <t>RULE-SEC-299</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #299: Identify leaks matching SMTP Password check</t>
-  </si>
-  <si>
-    <t>RULE-SEC-300</t>
-  </si>
-  <si>
-    <t>Gitleaks full-history scanner signature rule #300: Identify leaks matching JWT validation check</t>
+    <t>Gitleaks full-history scanner signature rule #325: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-326</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #326: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-327</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #327: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-328</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #328: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-329</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #329: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-330</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #330: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-331</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #331: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-332</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #332: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-333</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #333: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-334</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #334: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-335</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #335: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-336</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #336: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-337</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #337: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-338</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #338: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-339</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #339: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-340</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #340: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-341</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #341: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-342</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #342: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-343</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #343: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-344</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #344: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-345</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #345: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-346</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #346: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-347</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #347: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-348</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #348: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-349</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #349: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-350</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #350: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-351</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #351: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-352</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #352: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-353</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #353: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-354</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #354: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-355</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #355: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-356</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #356: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-357</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #357: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-358</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #358: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-359</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #359: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-360</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #360: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-361</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #361: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-362</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #362: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-363</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #363: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-364</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #364: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-365</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #365: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-366</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #366: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-367</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #367: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-368</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #368: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-369</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #369: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-370</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #370: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-371</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #371: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-372</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #372: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-373</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #373: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-374</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #374: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-375</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #375: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-376</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #376: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-377</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #377: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-378</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #378: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-379</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #379: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-380</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #380: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-381</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #381: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-382</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #382: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-383</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #383: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-384</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #384: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-385</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #385: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-386</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #386: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-387</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #387: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-388</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #388: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-389</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #389: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-390</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #390: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-391</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #391: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-392</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #392: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-393</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #393: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-394</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #394: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-395</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #395: Identify leaks matching JWT validation check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-396</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #396: Identify leaks matching MongoDB URI credentials</t>
+  </si>
+  <si>
+    <t>RULE-SEC-397</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #397: Identify leaks matching PrivateKey header search</t>
+  </si>
+  <si>
+    <t>RULE-SEC-398</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #398: Identify leaks matching GitHub Token signature</t>
+  </si>
+  <si>
+    <t>RULE-SEC-399</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #399: Identify leaks matching SMTP Password check</t>
+  </si>
+  <si>
+    <t>RULE-SEC-400</t>
+  </si>
+  <si>
+    <t>Gitleaks full-history scanner signature rule #400: Identify leaks matching JWT validation check</t>
   </si>
 </sst>
 </file>
@@ -3014,7 +3614,7 @@
         <v>70</v>
       </c>
       <c r="B4">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3097,7 +3697,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -5678,13 +6278,13 @@
         <v>399</v>
       </c>
       <c r="B152" t="s">
+        <v>87</v>
+      </c>
+      <c r="C152" t="s">
+        <v>88</v>
+      </c>
+      <c r="D152" t="s">
         <v>400</v>
-      </c>
-      <c r="C152" t="s">
-        <v>401</v>
-      </c>
-      <c r="D152" t="s">
-        <v>402</v>
       </c>
       <c r="E152" s="8" t="s">
         <v>118</v>
@@ -5692,16 +6292,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B153" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>404</v>
+        <v>92</v>
       </c>
       <c r="D153" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E153" s="8" t="s">
         <v>118</v>
@@ -5709,16 +6309,16 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B154" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>407</v>
+        <v>95</v>
       </c>
       <c r="D154" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E154" s="8" t="s">
         <v>118</v>
@@ -5726,16 +6326,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B155" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="D155" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E155" s="8" t="s">
         <v>118</v>
@@ -5743,16 +6343,16 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B156" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="D156" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E156" s="8" t="s">
         <v>118</v>
@@ -5760,16 +6360,16 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B157" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C157" t="s">
-        <v>401</v>
+        <v>104</v>
       </c>
       <c r="D157" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>118</v>
@@ -5777,16 +6377,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B158" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C158" t="s">
-        <v>404</v>
+        <v>107</v>
       </c>
       <c r="D158" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E158" s="8" t="s">
         <v>118</v>
@@ -5794,16 +6394,16 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B159" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C159" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E159" s="8" t="s">
         <v>118</v>
@@ -5811,16 +6411,16 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B160" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C160" t="s">
-        <v>410</v>
+        <v>113</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E160" s="8" t="s">
         <v>118</v>
@@ -5828,16 +6428,16 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B161" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C161" t="s">
-        <v>413</v>
+        <v>116</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>118</v>
@@ -5845,16 +6445,16 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B162" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C162" t="s">
-        <v>401</v>
+        <v>88</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E162" s="8" t="s">
         <v>118</v>
@@ -5862,16 +6462,16 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B163" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C163" t="s">
-        <v>404</v>
+        <v>92</v>
       </c>
       <c r="D163" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E163" s="8" t="s">
         <v>118</v>
@@ -5879,16 +6479,16 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B164" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C164" t="s">
-        <v>407</v>
+        <v>95</v>
       </c>
       <c r="D164" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E164" s="8" t="s">
         <v>118</v>
@@ -5896,16 +6496,16 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B165" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C165" t="s">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E165" s="8" t="s">
         <v>118</v>
@@ -5913,16 +6513,16 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B166" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C166" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="D166" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E166" s="8" t="s">
         <v>118</v>
@@ -5930,16 +6530,16 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B167" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C167" t="s">
-        <v>401</v>
+        <v>104</v>
       </c>
       <c r="D167" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="E167" s="8" t="s">
         <v>118</v>
@@ -5947,16 +6547,16 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B168" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C168" t="s">
-        <v>404</v>
+        <v>107</v>
       </c>
       <c r="D168" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E168" s="8" t="s">
         <v>118</v>
@@ -5964,16 +6564,16 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B169" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C169" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
       <c r="D169" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E169" s="8" t="s">
         <v>118</v>
@@ -5981,16 +6581,16 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B170" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C170" t="s">
-        <v>410</v>
+        <v>113</v>
       </c>
       <c r="D170" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E170" s="8" t="s">
         <v>118</v>
@@ -5998,16 +6598,16 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B171" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C171" t="s">
-        <v>413</v>
+        <v>116</v>
       </c>
       <c r="D171" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E171" s="8" t="s">
         <v>118</v>
@@ -6015,16 +6615,16 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B172" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C172" t="s">
-        <v>401</v>
+        <v>88</v>
       </c>
       <c r="D172" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E172" s="8" t="s">
         <v>118</v>
@@ -6032,16 +6632,16 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B173" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C173" t="s">
-        <v>404</v>
+        <v>92</v>
       </c>
       <c r="D173" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E173" s="8" t="s">
         <v>118</v>
@@ -6049,16 +6649,16 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B174" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C174" t="s">
-        <v>407</v>
+        <v>95</v>
       </c>
       <c r="D174" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E174" s="8" t="s">
         <v>118</v>
@@ -6066,16 +6666,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B175" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C175" t="s">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="D175" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E175" s="8" t="s">
         <v>118</v>
@@ -6083,16 +6683,16 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B176" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C176" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="D176" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E176" s="8" t="s">
         <v>118</v>
@@ -6100,16 +6700,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B177" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C177" t="s">
-        <v>401</v>
+        <v>104</v>
       </c>
       <c r="D177" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E177" s="8" t="s">
         <v>118</v>
@@ -6117,16 +6717,16 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B178" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C178" t="s">
-        <v>404</v>
+        <v>107</v>
       </c>
       <c r="D178" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="E178" s="8" t="s">
         <v>118</v>
@@ -6134,16 +6734,16 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B179" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C179" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
       <c r="D179" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E179" s="8" t="s">
         <v>118</v>
@@ -6151,16 +6751,16 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B180" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C180" t="s">
-        <v>410</v>
+        <v>113</v>
       </c>
       <c r="D180" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="E180" s="8" t="s">
         <v>118</v>
@@ -6168,16 +6768,16 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B181" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C181" t="s">
-        <v>413</v>
+        <v>116</v>
       </c>
       <c r="D181" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E181" s="8" t="s">
         <v>118</v>
@@ -6185,16 +6785,16 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B182" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C182" t="s">
-        <v>401</v>
+        <v>88</v>
       </c>
       <c r="D182" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E182" s="8" t="s">
         <v>118</v>
@@ -6202,16 +6802,16 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B183" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C183" t="s">
-        <v>404</v>
+        <v>92</v>
       </c>
       <c r="D183" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="E183" s="8" t="s">
         <v>118</v>
@@ -6219,16 +6819,16 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B184" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C184" t="s">
-        <v>407</v>
+        <v>95</v>
       </c>
       <c r="D184" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="E184" s="8" t="s">
         <v>118</v>
@@ -6236,16 +6836,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B185" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C185" t="s">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="D185" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E185" s="8" t="s">
         <v>118</v>
@@ -6253,16 +6853,16 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B186" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C186" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="D186" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="E186" s="8" t="s">
         <v>118</v>
@@ -6270,16 +6870,16 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B187" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C187" t="s">
-        <v>401</v>
+        <v>104</v>
       </c>
       <c r="D187" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E187" s="8" t="s">
         <v>118</v>
@@ -6287,16 +6887,16 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B188" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C188" t="s">
-        <v>404</v>
+        <v>107</v>
       </c>
       <c r="D188" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E188" s="8" t="s">
         <v>118</v>
@@ -6304,16 +6904,16 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B189" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C189" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
       <c r="D189" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E189" s="8" t="s">
         <v>118</v>
@@ -6321,16 +6921,16 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B190" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C190" t="s">
-        <v>410</v>
+        <v>113</v>
       </c>
       <c r="D190" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="E190" s="8" t="s">
         <v>118</v>
@@ -6338,16 +6938,16 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B191" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C191" t="s">
-        <v>413</v>
+        <v>116</v>
       </c>
       <c r="D191" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="E191" s="8" t="s">
         <v>118</v>
@@ -6355,16 +6955,16 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B192" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C192" t="s">
-        <v>401</v>
+        <v>88</v>
       </c>
       <c r="D192" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="E192" s="8" t="s">
         <v>118</v>
@@ -6372,16 +6972,16 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B193" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C193" t="s">
-        <v>404</v>
+        <v>92</v>
       </c>
       <c r="D193" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E193" s="8" t="s">
         <v>118</v>
@@ -6389,16 +6989,16 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B194" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C194" t="s">
-        <v>407</v>
+        <v>95</v>
       </c>
       <c r="D194" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E194" s="8" t="s">
         <v>118</v>
@@ -6406,16 +7006,16 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B195" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C195" t="s">
-        <v>410</v>
+        <v>98</v>
       </c>
       <c r="D195" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E195" s="8" t="s">
         <v>118</v>
@@ -6423,16 +7023,16 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B196" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C196" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="D196" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E196" s="8" t="s">
         <v>118</v>
@@ -6440,16 +7040,16 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B197" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C197" t="s">
-        <v>401</v>
+        <v>104</v>
       </c>
       <c r="D197" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E197" s="8" t="s">
         <v>118</v>
@@ -6457,16 +7057,16 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B198" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C198" t="s">
-        <v>404</v>
+        <v>107</v>
       </c>
       <c r="D198" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E198" s="8" t="s">
         <v>118</v>
@@ -6474,16 +7074,16 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B199" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C199" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
       <c r="D199" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E199" s="8" t="s">
         <v>118</v>
@@ -6491,16 +7091,16 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B200" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C200" t="s">
-        <v>410</v>
+        <v>113</v>
       </c>
       <c r="D200" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E200" s="8" t="s">
         <v>118</v>
@@ -6508,16 +7108,16 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B201" t="s">
-        <v>400</v>
+        <v>87</v>
       </c>
       <c r="C201" t="s">
-        <v>413</v>
+        <v>116</v>
       </c>
       <c r="D201" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="E201" s="8" t="s">
         <v>118</v>
@@ -6525,16 +7125,16 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B202" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C202" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D202" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E202" s="8" t="s">
         <v>118</v>
@@ -6542,16 +7142,16 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B203" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C203" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D203" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E203" s="8" t="s">
         <v>118</v>
@@ -6559,16 +7159,16 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B204" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C204" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D204" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E204" s="8" t="s">
         <v>118</v>
@@ -6576,16 +7176,16 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>509</v>
+      </c>
+      <c r="B205" t="s">
+        <v>500</v>
+      </c>
+      <c r="C205" t="s">
+        <v>510</v>
+      </c>
+      <c r="D205" t="s">
         <v>511</v>
-      </c>
-      <c r="B205" t="s">
-        <v>400</v>
-      </c>
-      <c r="C205" t="s">
-        <v>410</v>
-      </c>
-      <c r="D205" t="s">
-        <v>512</v>
       </c>
       <c r="E205" s="8" t="s">
         <v>118</v>
@@ -6593,13 +7193,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>512</v>
+      </c>
+      <c r="B206" t="s">
+        <v>500</v>
+      </c>
+      <c r="C206" t="s">
         <v>513</v>
-      </c>
-      <c r="B206" t="s">
-        <v>400</v>
-      </c>
-      <c r="C206" t="s">
-        <v>413</v>
       </c>
       <c r="D206" t="s">
         <v>514</v>
@@ -6613,10 +7213,10 @@
         <v>515</v>
       </c>
       <c r="B207" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C207" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D207" t="s">
         <v>516</v>
@@ -6630,10 +7230,10 @@
         <v>517</v>
       </c>
       <c r="B208" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C208" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D208" t="s">
         <v>518</v>
@@ -6647,10 +7247,10 @@
         <v>519</v>
       </c>
       <c r="B209" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C209" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D209" t="s">
         <v>520</v>
@@ -6664,10 +7264,10 @@
         <v>521</v>
       </c>
       <c r="B210" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C210" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D210" t="s">
         <v>522</v>
@@ -6681,10 +7281,10 @@
         <v>523</v>
       </c>
       <c r="B211" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C211" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D211" t="s">
         <v>524</v>
@@ -6698,10 +7298,10 @@
         <v>525</v>
       </c>
       <c r="B212" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C212" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D212" t="s">
         <v>526</v>
@@ -6715,10 +7315,10 @@
         <v>527</v>
       </c>
       <c r="B213" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C213" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D213" t="s">
         <v>528</v>
@@ -6732,10 +7332,10 @@
         <v>529</v>
       </c>
       <c r="B214" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C214" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D214" t="s">
         <v>530</v>
@@ -6749,10 +7349,10 @@
         <v>531</v>
       </c>
       <c r="B215" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C215" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D215" t="s">
         <v>532</v>
@@ -6766,10 +7366,10 @@
         <v>533</v>
       </c>
       <c r="B216" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C216" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D216" t="s">
         <v>534</v>
@@ -6783,10 +7383,10 @@
         <v>535</v>
       </c>
       <c r="B217" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C217" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D217" t="s">
         <v>536</v>
@@ -6800,10 +7400,10 @@
         <v>537</v>
       </c>
       <c r="B218" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C218" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D218" t="s">
         <v>538</v>
@@ -6817,10 +7417,10 @@
         <v>539</v>
       </c>
       <c r="B219" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C219" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D219" t="s">
         <v>540</v>
@@ -6834,10 +7434,10 @@
         <v>541</v>
       </c>
       <c r="B220" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C220" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D220" t="s">
         <v>542</v>
@@ -6851,10 +7451,10 @@
         <v>543</v>
       </c>
       <c r="B221" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C221" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D221" t="s">
         <v>544</v>
@@ -6868,10 +7468,10 @@
         <v>545</v>
       </c>
       <c r="B222" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C222" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D222" t="s">
         <v>546</v>
@@ -6885,10 +7485,10 @@
         <v>547</v>
       </c>
       <c r="B223" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C223" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D223" t="s">
         <v>548</v>
@@ -6902,10 +7502,10 @@
         <v>549</v>
       </c>
       <c r="B224" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C224" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D224" t="s">
         <v>550</v>
@@ -6919,10 +7519,10 @@
         <v>551</v>
       </c>
       <c r="B225" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C225" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D225" t="s">
         <v>552</v>
@@ -6936,10 +7536,10 @@
         <v>553</v>
       </c>
       <c r="B226" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C226" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D226" t="s">
         <v>554</v>
@@ -6953,10 +7553,10 @@
         <v>555</v>
       </c>
       <c r="B227" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C227" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D227" t="s">
         <v>556</v>
@@ -6970,10 +7570,10 @@
         <v>557</v>
       </c>
       <c r="B228" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C228" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D228" t="s">
         <v>558</v>
@@ -6987,10 +7587,10 @@
         <v>559</v>
       </c>
       <c r="B229" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C229" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D229" t="s">
         <v>560</v>
@@ -7004,10 +7604,10 @@
         <v>561</v>
       </c>
       <c r="B230" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C230" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D230" t="s">
         <v>562</v>
@@ -7021,10 +7621,10 @@
         <v>563</v>
       </c>
       <c r="B231" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C231" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D231" t="s">
         <v>564</v>
@@ -7038,10 +7638,10 @@
         <v>565</v>
       </c>
       <c r="B232" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C232" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D232" t="s">
         <v>566</v>
@@ -7055,10 +7655,10 @@
         <v>567</v>
       </c>
       <c r="B233" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C233" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D233" t="s">
         <v>568</v>
@@ -7072,10 +7672,10 @@
         <v>569</v>
       </c>
       <c r="B234" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C234" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D234" t="s">
         <v>570</v>
@@ -7089,10 +7689,10 @@
         <v>571</v>
       </c>
       <c r="B235" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C235" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D235" t="s">
         <v>572</v>
@@ -7106,10 +7706,10 @@
         <v>573</v>
       </c>
       <c r="B236" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C236" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D236" t="s">
         <v>574</v>
@@ -7123,10 +7723,10 @@
         <v>575</v>
       </c>
       <c r="B237" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C237" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D237" t="s">
         <v>576</v>
@@ -7140,10 +7740,10 @@
         <v>577</v>
       </c>
       <c r="B238" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C238" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D238" t="s">
         <v>578</v>
@@ -7157,10 +7757,10 @@
         <v>579</v>
       </c>
       <c r="B239" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C239" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D239" t="s">
         <v>580</v>
@@ -7174,10 +7774,10 @@
         <v>581</v>
       </c>
       <c r="B240" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C240" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D240" t="s">
         <v>582</v>
@@ -7191,10 +7791,10 @@
         <v>583</v>
       </c>
       <c r="B241" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C241" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D241" t="s">
         <v>584</v>
@@ -7208,10 +7808,10 @@
         <v>585</v>
       </c>
       <c r="B242" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C242" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D242" t="s">
         <v>586</v>
@@ -7225,10 +7825,10 @@
         <v>587</v>
       </c>
       <c r="B243" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C243" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D243" t="s">
         <v>588</v>
@@ -7242,10 +7842,10 @@
         <v>589</v>
       </c>
       <c r="B244" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C244" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D244" t="s">
         <v>590</v>
@@ -7259,10 +7859,10 @@
         <v>591</v>
       </c>
       <c r="B245" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C245" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D245" t="s">
         <v>592</v>
@@ -7276,10 +7876,10 @@
         <v>593</v>
       </c>
       <c r="B246" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C246" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D246" t="s">
         <v>594</v>
@@ -7293,10 +7893,10 @@
         <v>595</v>
       </c>
       <c r="B247" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C247" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="D247" t="s">
         <v>596</v>
@@ -7310,10 +7910,10 @@
         <v>597</v>
       </c>
       <c r="B248" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C248" t="s">
-        <v>404</v>
+        <v>504</v>
       </c>
       <c r="D248" t="s">
         <v>598</v>
@@ -7327,10 +7927,10 @@
         <v>599</v>
       </c>
       <c r="B249" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C249" t="s">
-        <v>407</v>
+        <v>507</v>
       </c>
       <c r="D249" t="s">
         <v>600</v>
@@ -7344,10 +7944,10 @@
         <v>601</v>
       </c>
       <c r="B250" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C250" t="s">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="D250" t="s">
         <v>602</v>
@@ -7361,10 +7961,10 @@
         <v>603</v>
       </c>
       <c r="B251" t="s">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C251" t="s">
-        <v>413</v>
+        <v>513</v>
       </c>
       <c r="D251" t="s">
         <v>604</v>
@@ -7378,13 +7978,13 @@
         <v>605</v>
       </c>
       <c r="B252" t="s">
+        <v>500</v>
+      </c>
+      <c r="C252" t="s">
+        <v>501</v>
+      </c>
+      <c r="D252" t="s">
         <v>606</v>
-      </c>
-      <c r="C252" t="s">
-        <v>607</v>
-      </c>
-      <c r="D252" t="s">
-        <v>608</v>
       </c>
       <c r="E252" s="8" t="s">
         <v>118</v>
@@ -7392,16 +7992,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B253" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C253" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D253" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E253" s="8" t="s">
         <v>118</v>
@@ -7409,16 +8009,16 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B254" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C254" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D254" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E254" s="8" t="s">
         <v>118</v>
@@ -7426,16 +8026,16 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B255" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C255" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D255" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E255" s="8" t="s">
         <v>118</v>
@@ -7443,16 +8043,16 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B256" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C256" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D256" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="E256" s="8" t="s">
         <v>118</v>
@@ -7460,16 +8060,16 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B257" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C257" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D257" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="E257" s="8" t="s">
         <v>118</v>
@@ -7477,16 +8077,16 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B258" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C258" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D258" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="E258" s="8" t="s">
         <v>118</v>
@@ -7494,16 +8094,16 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B259" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C259" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D259" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="E259" s="8" t="s">
         <v>118</v>
@@ -7511,16 +8111,16 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B260" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C260" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D260" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E260" s="8" t="s">
         <v>118</v>
@@ -7528,16 +8128,16 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B261" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C261" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D261" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="E261" s="8" t="s">
         <v>118</v>
@@ -7545,16 +8145,16 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B262" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C262" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D262" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="E262" s="8" t="s">
         <v>118</v>
@@ -7562,16 +8162,16 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="B263" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C263" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D263" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="E263" s="8" t="s">
         <v>118</v>
@@ -7579,16 +8179,16 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="B264" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C264" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D264" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="E264" s="8" t="s">
         <v>118</v>
@@ -7596,16 +8196,16 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B265" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C265" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D265" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="E265" s="8" t="s">
         <v>118</v>
@@ -7613,16 +8213,16 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B266" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C266" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D266" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E266" s="8" t="s">
         <v>118</v>
@@ -7630,16 +8230,16 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B267" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C267" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D267" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="E267" s="8" t="s">
         <v>118</v>
@@ -7647,16 +8247,16 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="B268" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C268" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D268" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="E268" s="8" t="s">
         <v>118</v>
@@ -7664,16 +8264,16 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B269" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C269" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D269" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E269" s="8" t="s">
         <v>118</v>
@@ -7681,16 +8281,16 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B270" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C270" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D270" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E270" s="8" t="s">
         <v>118</v>
@@ -7698,16 +8298,16 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B271" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C271" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D271" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="E271" s="8" t="s">
         <v>118</v>
@@ -7715,16 +8315,16 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B272" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C272" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D272" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E272" s="8" t="s">
         <v>118</v>
@@ -7732,16 +8332,16 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B273" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C273" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D273" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="E273" s="8" t="s">
         <v>118</v>
@@ -7749,16 +8349,16 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B274" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C274" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D274" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="E274" s="8" t="s">
         <v>118</v>
@@ -7766,16 +8366,16 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B275" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C275" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D275" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E275" s="8" t="s">
         <v>118</v>
@@ -7783,16 +8383,16 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B276" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C276" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D276" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="E276" s="8" t="s">
         <v>118</v>
@@ -7800,16 +8400,16 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B277" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C277" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D277" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="E277" s="8" t="s">
         <v>118</v>
@@ -7817,16 +8417,16 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="B278" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C278" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D278" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E278" s="8" t="s">
         <v>118</v>
@@ -7834,16 +8434,16 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B279" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C279" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D279" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E279" s="8" t="s">
         <v>118</v>
@@ -7851,16 +8451,16 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B280" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C280" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D280" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="E280" s="8" t="s">
         <v>118</v>
@@ -7868,16 +8468,16 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="B281" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C281" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D281" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E281" s="8" t="s">
         <v>118</v>
@@ -7885,16 +8485,16 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="B282" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C282" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D282" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="E282" s="8" t="s">
         <v>118</v>
@@ -7902,16 +8502,16 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B283" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C283" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D283" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="E283" s="8" t="s">
         <v>118</v>
@@ -7919,16 +8519,16 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="B284" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C284" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D284" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E284" s="8" t="s">
         <v>118</v>
@@ -7936,16 +8536,16 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B285" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C285" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D285" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E285" s="8" t="s">
         <v>118</v>
@@ -7953,16 +8553,16 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B286" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C286" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D286" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="E286" s="8" t="s">
         <v>118</v>
@@ -7970,16 +8570,16 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="B287" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C287" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D287" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="E287" s="8" t="s">
         <v>118</v>
@@ -7987,16 +8587,16 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="B288" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C288" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D288" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E288" s="8" t="s">
         <v>118</v>
@@ -8004,16 +8604,16 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="B289" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C289" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D289" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E289" s="8" t="s">
         <v>118</v>
@@ -8021,16 +8621,16 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B290" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C290" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D290" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="E290" s="8" t="s">
         <v>118</v>
@@ -8038,16 +8638,16 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B291" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C291" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D291" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="E291" s="8" t="s">
         <v>118</v>
@@ -8055,16 +8655,16 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B292" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C292" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D292" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="E292" s="8" t="s">
         <v>118</v>
@@ -8072,16 +8672,16 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="B293" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C293" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D293" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E293" s="8" t="s">
         <v>118</v>
@@ -8089,16 +8689,16 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="B294" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C294" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D294" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E294" s="8" t="s">
         <v>118</v>
@@ -8106,16 +8706,16 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B295" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C295" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D295" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="E295" s="8" t="s">
         <v>118</v>
@@ -8123,16 +8723,16 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="B296" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C296" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
       <c r="D296" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E296" s="8" t="s">
         <v>118</v>
@@ -8140,16 +8740,16 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B297" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C297" t="s">
-        <v>607</v>
+        <v>501</v>
       </c>
       <c r="D297" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E297" s="8" t="s">
         <v>118</v>
@@ -8157,16 +8757,16 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B298" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C298" t="s">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="D298" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="E298" s="8" t="s">
         <v>118</v>
@@ -8174,16 +8774,16 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="B299" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C299" t="s">
-        <v>613</v>
+        <v>507</v>
       </c>
       <c r="D299" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E299" s="8" t="s">
         <v>118</v>
@@ -8191,16 +8791,16 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="B300" t="s">
-        <v>606</v>
+        <v>500</v>
       </c>
       <c r="C300" t="s">
-        <v>616</v>
+        <v>510</v>
       </c>
       <c r="D300" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E300" s="8" t="s">
         <v>118</v>
@@ -8208,18 +8808,1718 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
+        <v>703</v>
+      </c>
+      <c r="B301" t="s">
+        <v>500</v>
+      </c>
+      <c r="C301" t="s">
+        <v>513</v>
+      </c>
+      <c r="D301" t="s">
+        <v>704</v>
+      </c>
+      <c r="E301" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>705</v>
+      </c>
+      <c r="B302" t="s">
+        <v>500</v>
+      </c>
+      <c r="C302" t="s">
+        <v>501</v>
+      </c>
+      <c r="D302" t="s">
+        <v>706</v>
+      </c>
+      <c r="E302" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>707</v>
+      </c>
+      <c r="B303" t="s">
+        <v>500</v>
+      </c>
+      <c r="C303" t="s">
+        <v>504</v>
+      </c>
+      <c r="D303" t="s">
+        <v>708</v>
+      </c>
+      <c r="E303" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
         <v>709</v>
       </c>
-      <c r="B301" t="s">
-        <v>606</v>
-      </c>
-      <c r="C301" t="s">
-        <v>619</v>
-      </c>
-      <c r="D301" t="s">
+      <c r="B304" t="s">
+        <v>500</v>
+      </c>
+      <c r="C304" t="s">
+        <v>507</v>
+      </c>
+      <c r="D304" t="s">
         <v>710</v>
       </c>
-      <c r="E301" s="8" t="s">
+      <c r="E304" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>711</v>
+      </c>
+      <c r="B305" t="s">
+        <v>500</v>
+      </c>
+      <c r="C305" t="s">
+        <v>510</v>
+      </c>
+      <c r="D305" t="s">
+        <v>712</v>
+      </c>
+      <c r="E305" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>713</v>
+      </c>
+      <c r="B306" t="s">
+        <v>500</v>
+      </c>
+      <c r="C306" t="s">
+        <v>513</v>
+      </c>
+      <c r="D306" t="s">
+        <v>714</v>
+      </c>
+      <c r="E306" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>715</v>
+      </c>
+      <c r="B307" t="s">
+        <v>500</v>
+      </c>
+      <c r="C307" t="s">
+        <v>501</v>
+      </c>
+      <c r="D307" t="s">
+        <v>716</v>
+      </c>
+      <c r="E307" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>717</v>
+      </c>
+      <c r="B308" t="s">
+        <v>500</v>
+      </c>
+      <c r="C308" t="s">
+        <v>504</v>
+      </c>
+      <c r="D308" t="s">
+        <v>718</v>
+      </c>
+      <c r="E308" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>719</v>
+      </c>
+      <c r="B309" t="s">
+        <v>500</v>
+      </c>
+      <c r="C309" t="s">
+        <v>507</v>
+      </c>
+      <c r="D309" t="s">
+        <v>720</v>
+      </c>
+      <c r="E309" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>721</v>
+      </c>
+      <c r="B310" t="s">
+        <v>500</v>
+      </c>
+      <c r="C310" t="s">
+        <v>510</v>
+      </c>
+      <c r="D310" t="s">
+        <v>722</v>
+      </c>
+      <c r="E310" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>723</v>
+      </c>
+      <c r="B311" t="s">
+        <v>500</v>
+      </c>
+      <c r="C311" t="s">
+        <v>513</v>
+      </c>
+      <c r="D311" t="s">
+        <v>724</v>
+      </c>
+      <c r="E311" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>725</v>
+      </c>
+      <c r="B312" t="s">
+        <v>500</v>
+      </c>
+      <c r="C312" t="s">
+        <v>501</v>
+      </c>
+      <c r="D312" t="s">
+        <v>726</v>
+      </c>
+      <c r="E312" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>727</v>
+      </c>
+      <c r="B313" t="s">
+        <v>500</v>
+      </c>
+      <c r="C313" t="s">
+        <v>504</v>
+      </c>
+      <c r="D313" t="s">
+        <v>728</v>
+      </c>
+      <c r="E313" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>729</v>
+      </c>
+      <c r="B314" t="s">
+        <v>500</v>
+      </c>
+      <c r="C314" t="s">
+        <v>507</v>
+      </c>
+      <c r="D314" t="s">
+        <v>730</v>
+      </c>
+      <c r="E314" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>731</v>
+      </c>
+      <c r="B315" t="s">
+        <v>500</v>
+      </c>
+      <c r="C315" t="s">
+        <v>510</v>
+      </c>
+      <c r="D315" t="s">
+        <v>732</v>
+      </c>
+      <c r="E315" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>733</v>
+      </c>
+      <c r="B316" t="s">
+        <v>500</v>
+      </c>
+      <c r="C316" t="s">
+        <v>513</v>
+      </c>
+      <c r="D316" t="s">
+        <v>734</v>
+      </c>
+      <c r="E316" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>735</v>
+      </c>
+      <c r="B317" t="s">
+        <v>500</v>
+      </c>
+      <c r="C317" t="s">
+        <v>501</v>
+      </c>
+      <c r="D317" t="s">
+        <v>736</v>
+      </c>
+      <c r="E317" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>737</v>
+      </c>
+      <c r="B318" t="s">
+        <v>500</v>
+      </c>
+      <c r="C318" t="s">
+        <v>504</v>
+      </c>
+      <c r="D318" t="s">
+        <v>738</v>
+      </c>
+      <c r="E318" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>739</v>
+      </c>
+      <c r="B319" t="s">
+        <v>500</v>
+      </c>
+      <c r="C319" t="s">
+        <v>507</v>
+      </c>
+      <c r="D319" t="s">
+        <v>740</v>
+      </c>
+      <c r="E319" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>741</v>
+      </c>
+      <c r="B320" t="s">
+        <v>500</v>
+      </c>
+      <c r="C320" t="s">
+        <v>510</v>
+      </c>
+      <c r="D320" t="s">
+        <v>742</v>
+      </c>
+      <c r="E320" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>743</v>
+      </c>
+      <c r="B321" t="s">
+        <v>500</v>
+      </c>
+      <c r="C321" t="s">
+        <v>513</v>
+      </c>
+      <c r="D321" t="s">
+        <v>744</v>
+      </c>
+      <c r="E321" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>745</v>
+      </c>
+      <c r="B322" t="s">
+        <v>746</v>
+      </c>
+      <c r="C322" t="s">
+        <v>747</v>
+      </c>
+      <c r="D322" t="s">
+        <v>748</v>
+      </c>
+      <c r="E322" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>749</v>
+      </c>
+      <c r="B323" t="s">
+        <v>746</v>
+      </c>
+      <c r="C323" t="s">
+        <v>750</v>
+      </c>
+      <c r="D323" t="s">
+        <v>751</v>
+      </c>
+      <c r="E323" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>752</v>
+      </c>
+      <c r="B324" t="s">
+        <v>746</v>
+      </c>
+      <c r="C324" t="s">
+        <v>753</v>
+      </c>
+      <c r="D324" t="s">
+        <v>754</v>
+      </c>
+      <c r="E324" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>755</v>
+      </c>
+      <c r="B325" t="s">
+        <v>746</v>
+      </c>
+      <c r="C325" t="s">
+        <v>756</v>
+      </c>
+      <c r="D325" t="s">
+        <v>757</v>
+      </c>
+      <c r="E325" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>758</v>
+      </c>
+      <c r="B326" t="s">
+        <v>746</v>
+      </c>
+      <c r="C326" t="s">
+        <v>759</v>
+      </c>
+      <c r="D326" t="s">
+        <v>760</v>
+      </c>
+      <c r="E326" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>761</v>
+      </c>
+      <c r="B327" t="s">
+        <v>746</v>
+      </c>
+      <c r="C327" t="s">
+        <v>747</v>
+      </c>
+      <c r="D327" t="s">
+        <v>762</v>
+      </c>
+      <c r="E327" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>763</v>
+      </c>
+      <c r="B328" t="s">
+        <v>746</v>
+      </c>
+      <c r="C328" t="s">
+        <v>750</v>
+      </c>
+      <c r="D328" t="s">
+        <v>764</v>
+      </c>
+      <c r="E328" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>765</v>
+      </c>
+      <c r="B329" t="s">
+        <v>746</v>
+      </c>
+      <c r="C329" t="s">
+        <v>753</v>
+      </c>
+      <c r="D329" t="s">
+        <v>766</v>
+      </c>
+      <c r="E329" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>767</v>
+      </c>
+      <c r="B330" t="s">
+        <v>746</v>
+      </c>
+      <c r="C330" t="s">
+        <v>756</v>
+      </c>
+      <c r="D330" t="s">
+        <v>768</v>
+      </c>
+      <c r="E330" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>769</v>
+      </c>
+      <c r="B331" t="s">
+        <v>746</v>
+      </c>
+      <c r="C331" t="s">
+        <v>759</v>
+      </c>
+      <c r="D331" t="s">
+        <v>770</v>
+      </c>
+      <c r="E331" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>771</v>
+      </c>
+      <c r="B332" t="s">
+        <v>746</v>
+      </c>
+      <c r="C332" t="s">
+        <v>747</v>
+      </c>
+      <c r="D332" t="s">
+        <v>772</v>
+      </c>
+      <c r="E332" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>773</v>
+      </c>
+      <c r="B333" t="s">
+        <v>746</v>
+      </c>
+      <c r="C333" t="s">
+        <v>750</v>
+      </c>
+      <c r="D333" t="s">
+        <v>774</v>
+      </c>
+      <c r="E333" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>775</v>
+      </c>
+      <c r="B334" t="s">
+        <v>746</v>
+      </c>
+      <c r="C334" t="s">
+        <v>753</v>
+      </c>
+      <c r="D334" t="s">
+        <v>776</v>
+      </c>
+      <c r="E334" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>777</v>
+      </c>
+      <c r="B335" t="s">
+        <v>746</v>
+      </c>
+      <c r="C335" t="s">
+        <v>756</v>
+      </c>
+      <c r="D335" t="s">
+        <v>778</v>
+      </c>
+      <c r="E335" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>779</v>
+      </c>
+      <c r="B336" t="s">
+        <v>746</v>
+      </c>
+      <c r="C336" t="s">
+        <v>759</v>
+      </c>
+      <c r="D336" t="s">
+        <v>780</v>
+      </c>
+      <c r="E336" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>781</v>
+      </c>
+      <c r="B337" t="s">
+        <v>746</v>
+      </c>
+      <c r="C337" t="s">
+        <v>747</v>
+      </c>
+      <c r="D337" t="s">
+        <v>782</v>
+      </c>
+      <c r="E337" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>783</v>
+      </c>
+      <c r="B338" t="s">
+        <v>746</v>
+      </c>
+      <c r="C338" t="s">
+        <v>750</v>
+      </c>
+      <c r="D338" t="s">
+        <v>784</v>
+      </c>
+      <c r="E338" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>785</v>
+      </c>
+      <c r="B339" t="s">
+        <v>746</v>
+      </c>
+      <c r="C339" t="s">
+        <v>753</v>
+      </c>
+      <c r="D339" t="s">
+        <v>786</v>
+      </c>
+      <c r="E339" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>787</v>
+      </c>
+      <c r="B340" t="s">
+        <v>746</v>
+      </c>
+      <c r="C340" t="s">
+        <v>756</v>
+      </c>
+      <c r="D340" t="s">
+        <v>788</v>
+      </c>
+      <c r="E340" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>789</v>
+      </c>
+      <c r="B341" t="s">
+        <v>746</v>
+      </c>
+      <c r="C341" t="s">
+        <v>759</v>
+      </c>
+      <c r="D341" t="s">
+        <v>790</v>
+      </c>
+      <c r="E341" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>791</v>
+      </c>
+      <c r="B342" t="s">
+        <v>746</v>
+      </c>
+      <c r="C342" t="s">
+        <v>747</v>
+      </c>
+      <c r="D342" t="s">
+        <v>792</v>
+      </c>
+      <c r="E342" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>793</v>
+      </c>
+      <c r="B343" t="s">
+        <v>746</v>
+      </c>
+      <c r="C343" t="s">
+        <v>750</v>
+      </c>
+      <c r="D343" t="s">
+        <v>794</v>
+      </c>
+      <c r="E343" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>795</v>
+      </c>
+      <c r="B344" t="s">
+        <v>746</v>
+      </c>
+      <c r="C344" t="s">
+        <v>753</v>
+      </c>
+      <c r="D344" t="s">
+        <v>796</v>
+      </c>
+      <c r="E344" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>797</v>
+      </c>
+      <c r="B345" t="s">
+        <v>746</v>
+      </c>
+      <c r="C345" t="s">
+        <v>756</v>
+      </c>
+      <c r="D345" t="s">
+        <v>798</v>
+      </c>
+      <c r="E345" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>799</v>
+      </c>
+      <c r="B346" t="s">
+        <v>746</v>
+      </c>
+      <c r="C346" t="s">
+        <v>759</v>
+      </c>
+      <c r="D346" t="s">
+        <v>800</v>
+      </c>
+      <c r="E346" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>801</v>
+      </c>
+      <c r="B347" t="s">
+        <v>746</v>
+      </c>
+      <c r="C347" t="s">
+        <v>747</v>
+      </c>
+      <c r="D347" t="s">
+        <v>802</v>
+      </c>
+      <c r="E347" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>803</v>
+      </c>
+      <c r="B348" t="s">
+        <v>746</v>
+      </c>
+      <c r="C348" t="s">
+        <v>750</v>
+      </c>
+      <c r="D348" t="s">
+        <v>804</v>
+      </c>
+      <c r="E348" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>805</v>
+      </c>
+      <c r="B349" t="s">
+        <v>746</v>
+      </c>
+      <c r="C349" t="s">
+        <v>753</v>
+      </c>
+      <c r="D349" t="s">
+        <v>806</v>
+      </c>
+      <c r="E349" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>807</v>
+      </c>
+      <c r="B350" t="s">
+        <v>746</v>
+      </c>
+      <c r="C350" t="s">
+        <v>756</v>
+      </c>
+      <c r="D350" t="s">
+        <v>808</v>
+      </c>
+      <c r="E350" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>809</v>
+      </c>
+      <c r="B351" t="s">
+        <v>746</v>
+      </c>
+      <c r="C351" t="s">
+        <v>759</v>
+      </c>
+      <c r="D351" t="s">
+        <v>810</v>
+      </c>
+      <c r="E351" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>811</v>
+      </c>
+      <c r="B352" t="s">
+        <v>746</v>
+      </c>
+      <c r="C352" t="s">
+        <v>747</v>
+      </c>
+      <c r="D352" t="s">
+        <v>812</v>
+      </c>
+      <c r="E352" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>813</v>
+      </c>
+      <c r="B353" t="s">
+        <v>746</v>
+      </c>
+      <c r="C353" t="s">
+        <v>750</v>
+      </c>
+      <c r="D353" t="s">
+        <v>814</v>
+      </c>
+      <c r="E353" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>815</v>
+      </c>
+      <c r="B354" t="s">
+        <v>746</v>
+      </c>
+      <c r="C354" t="s">
+        <v>753</v>
+      </c>
+      <c r="D354" t="s">
+        <v>816</v>
+      </c>
+      <c r="E354" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>817</v>
+      </c>
+      <c r="B355" t="s">
+        <v>746</v>
+      </c>
+      <c r="C355" t="s">
+        <v>756</v>
+      </c>
+      <c r="D355" t="s">
+        <v>818</v>
+      </c>
+      <c r="E355" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>819</v>
+      </c>
+      <c r="B356" t="s">
+        <v>746</v>
+      </c>
+      <c r="C356" t="s">
+        <v>759</v>
+      </c>
+      <c r="D356" t="s">
+        <v>820</v>
+      </c>
+      <c r="E356" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>821</v>
+      </c>
+      <c r="B357" t="s">
+        <v>746</v>
+      </c>
+      <c r="C357" t="s">
+        <v>747</v>
+      </c>
+      <c r="D357" t="s">
+        <v>822</v>
+      </c>
+      <c r="E357" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>823</v>
+      </c>
+      <c r="B358" t="s">
+        <v>746</v>
+      </c>
+      <c r="C358" t="s">
+        <v>750</v>
+      </c>
+      <c r="D358" t="s">
+        <v>824</v>
+      </c>
+      <c r="E358" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>825</v>
+      </c>
+      <c r="B359" t="s">
+        <v>746</v>
+      </c>
+      <c r="C359" t="s">
+        <v>753</v>
+      </c>
+      <c r="D359" t="s">
+        <v>826</v>
+      </c>
+      <c r="E359" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>827</v>
+      </c>
+      <c r="B360" t="s">
+        <v>746</v>
+      </c>
+      <c r="C360" t="s">
+        <v>756</v>
+      </c>
+      <c r="D360" t="s">
+        <v>828</v>
+      </c>
+      <c r="E360" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>829</v>
+      </c>
+      <c r="B361" t="s">
+        <v>746</v>
+      </c>
+      <c r="C361" t="s">
+        <v>759</v>
+      </c>
+      <c r="D361" t="s">
+        <v>830</v>
+      </c>
+      <c r="E361" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>831</v>
+      </c>
+      <c r="B362" t="s">
+        <v>746</v>
+      </c>
+      <c r="C362" t="s">
+        <v>747</v>
+      </c>
+      <c r="D362" t="s">
+        <v>832</v>
+      </c>
+      <c r="E362" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>833</v>
+      </c>
+      <c r="B363" t="s">
+        <v>746</v>
+      </c>
+      <c r="C363" t="s">
+        <v>750</v>
+      </c>
+      <c r="D363" t="s">
+        <v>834</v>
+      </c>
+      <c r="E363" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>835</v>
+      </c>
+      <c r="B364" t="s">
+        <v>746</v>
+      </c>
+      <c r="C364" t="s">
+        <v>753</v>
+      </c>
+      <c r="D364" t="s">
+        <v>836</v>
+      </c>
+      <c r="E364" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>837</v>
+      </c>
+      <c r="B365" t="s">
+        <v>746</v>
+      </c>
+      <c r="C365" t="s">
+        <v>756</v>
+      </c>
+      <c r="D365" t="s">
+        <v>838</v>
+      </c>
+      <c r="E365" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>839</v>
+      </c>
+      <c r="B366" t="s">
+        <v>746</v>
+      </c>
+      <c r="C366" t="s">
+        <v>759</v>
+      </c>
+      <c r="D366" t="s">
+        <v>840</v>
+      </c>
+      <c r="E366" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>841</v>
+      </c>
+      <c r="B367" t="s">
+        <v>746</v>
+      </c>
+      <c r="C367" t="s">
+        <v>747</v>
+      </c>
+      <c r="D367" t="s">
+        <v>842</v>
+      </c>
+      <c r="E367" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>843</v>
+      </c>
+      <c r="B368" t="s">
+        <v>746</v>
+      </c>
+      <c r="C368" t="s">
+        <v>750</v>
+      </c>
+      <c r="D368" t="s">
+        <v>844</v>
+      </c>
+      <c r="E368" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>845</v>
+      </c>
+      <c r="B369" t="s">
+        <v>746</v>
+      </c>
+      <c r="C369" t="s">
+        <v>753</v>
+      </c>
+      <c r="D369" t="s">
+        <v>846</v>
+      </c>
+      <c r="E369" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>847</v>
+      </c>
+      <c r="B370" t="s">
+        <v>746</v>
+      </c>
+      <c r="C370" t="s">
+        <v>756</v>
+      </c>
+      <c r="D370" t="s">
+        <v>848</v>
+      </c>
+      <c r="E370" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>849</v>
+      </c>
+      <c r="B371" t="s">
+        <v>746</v>
+      </c>
+      <c r="C371" t="s">
+        <v>759</v>
+      </c>
+      <c r="D371" t="s">
+        <v>850</v>
+      </c>
+      <c r="E371" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>851</v>
+      </c>
+      <c r="B372" t="s">
+        <v>746</v>
+      </c>
+      <c r="C372" t="s">
+        <v>747</v>
+      </c>
+      <c r="D372" t="s">
+        <v>852</v>
+      </c>
+      <c r="E372" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>853</v>
+      </c>
+      <c r="B373" t="s">
+        <v>746</v>
+      </c>
+      <c r="C373" t="s">
+        <v>750</v>
+      </c>
+      <c r="D373" t="s">
+        <v>854</v>
+      </c>
+      <c r="E373" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>855</v>
+      </c>
+      <c r="B374" t="s">
+        <v>746</v>
+      </c>
+      <c r="C374" t="s">
+        <v>753</v>
+      </c>
+      <c r="D374" t="s">
+        <v>856</v>
+      </c>
+      <c r="E374" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>857</v>
+      </c>
+      <c r="B375" t="s">
+        <v>746</v>
+      </c>
+      <c r="C375" t="s">
+        <v>756</v>
+      </c>
+      <c r="D375" t="s">
+        <v>858</v>
+      </c>
+      <c r="E375" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>859</v>
+      </c>
+      <c r="B376" t="s">
+        <v>746</v>
+      </c>
+      <c r="C376" t="s">
+        <v>759</v>
+      </c>
+      <c r="D376" t="s">
+        <v>860</v>
+      </c>
+      <c r="E376" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>861</v>
+      </c>
+      <c r="B377" t="s">
+        <v>746</v>
+      </c>
+      <c r="C377" t="s">
+        <v>747</v>
+      </c>
+      <c r="D377" t="s">
+        <v>862</v>
+      </c>
+      <c r="E377" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>863</v>
+      </c>
+      <c r="B378" t="s">
+        <v>746</v>
+      </c>
+      <c r="C378" t="s">
+        <v>750</v>
+      </c>
+      <c r="D378" t="s">
+        <v>864</v>
+      </c>
+      <c r="E378" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>865</v>
+      </c>
+      <c r="B379" t="s">
+        <v>746</v>
+      </c>
+      <c r="C379" t="s">
+        <v>753</v>
+      </c>
+      <c r="D379" t="s">
+        <v>866</v>
+      </c>
+      <c r="E379" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>867</v>
+      </c>
+      <c r="B380" t="s">
+        <v>746</v>
+      </c>
+      <c r="C380" t="s">
+        <v>756</v>
+      </c>
+      <c r="D380" t="s">
+        <v>868</v>
+      </c>
+      <c r="E380" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>869</v>
+      </c>
+      <c r="B381" t="s">
+        <v>746</v>
+      </c>
+      <c r="C381" t="s">
+        <v>759</v>
+      </c>
+      <c r="D381" t="s">
+        <v>870</v>
+      </c>
+      <c r="E381" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>871</v>
+      </c>
+      <c r="B382" t="s">
+        <v>746</v>
+      </c>
+      <c r="C382" t="s">
+        <v>747</v>
+      </c>
+      <c r="D382" t="s">
+        <v>872</v>
+      </c>
+      <c r="E382" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>873</v>
+      </c>
+      <c r="B383" t="s">
+        <v>746</v>
+      </c>
+      <c r="C383" t="s">
+        <v>750</v>
+      </c>
+      <c r="D383" t="s">
+        <v>874</v>
+      </c>
+      <c r="E383" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>875</v>
+      </c>
+      <c r="B384" t="s">
+        <v>746</v>
+      </c>
+      <c r="C384" t="s">
+        <v>753</v>
+      </c>
+      <c r="D384" t="s">
+        <v>876</v>
+      </c>
+      <c r="E384" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>877</v>
+      </c>
+      <c r="B385" t="s">
+        <v>746</v>
+      </c>
+      <c r="C385" t="s">
+        <v>756</v>
+      </c>
+      <c r="D385" t="s">
+        <v>878</v>
+      </c>
+      <c r="E385" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>879</v>
+      </c>
+      <c r="B386" t="s">
+        <v>746</v>
+      </c>
+      <c r="C386" t="s">
+        <v>759</v>
+      </c>
+      <c r="D386" t="s">
+        <v>880</v>
+      </c>
+      <c r="E386" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>881</v>
+      </c>
+      <c r="B387" t="s">
+        <v>746</v>
+      </c>
+      <c r="C387" t="s">
+        <v>747</v>
+      </c>
+      <c r="D387" t="s">
+        <v>882</v>
+      </c>
+      <c r="E387" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>883</v>
+      </c>
+      <c r="B388" t="s">
+        <v>746</v>
+      </c>
+      <c r="C388" t="s">
+        <v>750</v>
+      </c>
+      <c r="D388" t="s">
+        <v>884</v>
+      </c>
+      <c r="E388" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>885</v>
+      </c>
+      <c r="B389" t="s">
+        <v>746</v>
+      </c>
+      <c r="C389" t="s">
+        <v>753</v>
+      </c>
+      <c r="D389" t="s">
+        <v>886</v>
+      </c>
+      <c r="E389" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>887</v>
+      </c>
+      <c r="B390" t="s">
+        <v>746</v>
+      </c>
+      <c r="C390" t="s">
+        <v>756</v>
+      </c>
+      <c r="D390" t="s">
+        <v>888</v>
+      </c>
+      <c r="E390" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>889</v>
+      </c>
+      <c r="B391" t="s">
+        <v>746</v>
+      </c>
+      <c r="C391" t="s">
+        <v>759</v>
+      </c>
+      <c r="D391" t="s">
+        <v>890</v>
+      </c>
+      <c r="E391" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>891</v>
+      </c>
+      <c r="B392" t="s">
+        <v>746</v>
+      </c>
+      <c r="C392" t="s">
+        <v>747</v>
+      </c>
+      <c r="D392" t="s">
+        <v>892</v>
+      </c>
+      <c r="E392" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>893</v>
+      </c>
+      <c r="B393" t="s">
+        <v>746</v>
+      </c>
+      <c r="C393" t="s">
+        <v>750</v>
+      </c>
+      <c r="D393" t="s">
+        <v>894</v>
+      </c>
+      <c r="E393" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>895</v>
+      </c>
+      <c r="B394" t="s">
+        <v>746</v>
+      </c>
+      <c r="C394" t="s">
+        <v>753</v>
+      </c>
+      <c r="D394" t="s">
+        <v>896</v>
+      </c>
+      <c r="E394" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>897</v>
+      </c>
+      <c r="B395" t="s">
+        <v>746</v>
+      </c>
+      <c r="C395" t="s">
+        <v>756</v>
+      </c>
+      <c r="D395" t="s">
+        <v>898</v>
+      </c>
+      <c r="E395" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>899</v>
+      </c>
+      <c r="B396" t="s">
+        <v>746</v>
+      </c>
+      <c r="C396" t="s">
+        <v>759</v>
+      </c>
+      <c r="D396" t="s">
+        <v>900</v>
+      </c>
+      <c r="E396" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>901</v>
+      </c>
+      <c r="B397" t="s">
+        <v>746</v>
+      </c>
+      <c r="C397" t="s">
+        <v>747</v>
+      </c>
+      <c r="D397" t="s">
+        <v>902</v>
+      </c>
+      <c r="E397" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>903</v>
+      </c>
+      <c r="B398" t="s">
+        <v>746</v>
+      </c>
+      <c r="C398" t="s">
+        <v>750</v>
+      </c>
+      <c r="D398" t="s">
+        <v>904</v>
+      </c>
+      <c r="E398" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>905</v>
+      </c>
+      <c r="B399" t="s">
+        <v>746</v>
+      </c>
+      <c r="C399" t="s">
+        <v>753</v>
+      </c>
+      <c r="D399" t="s">
+        <v>906</v>
+      </c>
+      <c r="E399" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>907</v>
+      </c>
+      <c r="B400" t="s">
+        <v>746</v>
+      </c>
+      <c r="C400" t="s">
+        <v>756</v>
+      </c>
+      <c r="D400" t="s">
+        <v>908</v>
+      </c>
+      <c r="E400" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>909</v>
+      </c>
+      <c r="B401" t="s">
+        <v>746</v>
+      </c>
+      <c r="C401" t="s">
+        <v>759</v>
+      </c>
+      <c r="D401" t="s">
+        <v>910</v>
+      </c>
+      <c r="E401" s="8" t="s">
         <v>118</v>
       </c>
     </row>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-23 10:06:42 UTC</t>
+    <t>2026-06-23 11:04:00 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-23 11:04:00 UTC</t>
+    <t>2026-06-23 11:27:20 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-06-23 11:27:20 UTC</t>
+    <t>2026-07-19 15:50:25 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-19 15:50:25 UTC</t>
+    <t>2026-07-19 16:35:46 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-19 16:35:46 UTC</t>
+    <t>2026-07-19 16:51:26 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-19 16:51:26 UTC</t>
+    <t>2026-07-19 17:49:41 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-19 17:49:41 UTC</t>
+    <t>2026-07-19 18:07:18 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-19 18:07:18 UTC</t>
+    <t>2026-07-22 05:51:26 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 05:51:26 UTC</t>
+    <t>2026-07-22 06:08:39 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 06:08:39 UTC</t>
+    <t>2026-07-22 06:26:02 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 06:26:02 UTC</t>
+    <t>2026-07-22 06:44:24 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 06:44:24 UTC</t>
+    <t>2026-07-22 07:02:36 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 07:02:36 UTC</t>
+    <t>2026-07-22 07:27:20 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 07:27:20 UTC</t>
+    <t>2026-07-22 07:44:58 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 07:44:58 UTC</t>
+    <t>2026-07-22 08:03:38 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>19</t>
+    <t>21</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 08:03:38 UTC</t>
+    <t>2026-07-22 08:15:35 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 08:15:35 UTC</t>
+    <t>2026-07-22 08:33:12 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 08:33:12 UTC</t>
+    <t>2026-07-22 08:49:34 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 08:49:34 UTC</t>
+    <t>2026-07-22 09:08:59 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>24</t>
+    <t>26</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 09:08:59 UTC</t>
+    <t>2026-07-22 09:28:04 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 09:28:04 UTC</t>
+    <t>2026-07-22 09:45:13 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>27</t>
+    <t>29</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 09:45:13 UTC</t>
+    <t>2026-07-22 10:03:16 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 10:03:16 UTC</t>
+    <t>2026-07-22 10:25:23 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>30</t>
+    <t>31</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 10:25:23 UTC</t>
+    <t>2026-07-22 10:44:41 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>31</t>
+    <t>32</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 10:44:41 UTC</t>
+    <t>2026-07-22 10:58:50 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>32</t>
+    <t>33</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-22 10:58:50 UTC</t>
+    <t>2026-07-23 08:51:07 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>33</t>
+    <t>34</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-23 08:51:07 UTC</t>
+    <t>2026-07-23 09:11:10 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>34</t>
+    <t>35</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-23 09:11:10 UTC</t>
+    <t>2026-07-23 09:13:55 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>35</t>
+    <t>36</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-23 09:13:55 UTC</t>
+    <t>2026-07-23 09:34:57 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -103,13 +103,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-23 13:46:26 UTC</t>
+    <t>2026-07-24 03:31:47 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>38</t>
+    <t>39</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>
